--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533505</v>
+        <v>130533496</v>
       </c>
       <c r="B4" t="n">
-        <v>91751</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -913,7 +917,7 @@
         <v>454216</v>
       </c>
       <c r="R4" t="n">
-        <v>6957270</v>
+        <v>6957337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533496</v>
+        <v>130533505</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>91751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +992,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1010,7 +1015,7 @@
         <v>454216</v>
       </c>
       <c r="R5" t="n">
-        <v>6957337</v>
+        <v>6957270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,11 +1048,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533497</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533498</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533496</v>
+        <v>130533505</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>91777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -917,7 +913,7 @@
         <v>454216</v>
       </c>
       <c r="R4" t="n">
-        <v>6957337</v>
+        <v>6957270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533505</v>
+        <v>130533496</v>
       </c>
       <c r="B5" t="n">
-        <v>91751</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1015,7 +1010,7 @@
         <v>454216</v>
       </c>
       <c r="R5" t="n">
-        <v>6957270</v>
+        <v>6957337</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,6 +1043,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>130533505</v>
       </c>
       <c r="B4" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>130533505</v>
       </c>
       <c r="B4" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533497</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533498</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533505</v>
+        <v>130533496</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -913,7 +917,7 @@
         <v>454216</v>
       </c>
       <c r="R4" t="n">
-        <v>6957270</v>
+        <v>6957337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533496</v>
+        <v>130533505</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>91781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +992,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1010,7 +1015,7 @@
         <v>454216</v>
       </c>
       <c r="R5" t="n">
-        <v>6957337</v>
+        <v>6957270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,11 +1048,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533496</v>
+        <v>130533505</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -917,7 +913,7 @@
         <v>454216</v>
       </c>
       <c r="R4" t="n">
-        <v>6957337</v>
+        <v>6957270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533505</v>
+        <v>130533496</v>
       </c>
       <c r="B5" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1015,7 +1010,7 @@
         <v>454216</v>
       </c>
       <c r="R5" t="n">
-        <v>6957270</v>
+        <v>6957337</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,6 +1043,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533497</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533498</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130533505</v>
       </c>
       <c r="B4" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>130533496</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533497</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533498</v>
       </c>
       <c r="B3" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533505</v>
+        <v>130533496</v>
       </c>
       <c r="B4" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -913,7 +917,7 @@
         <v>454216</v>
       </c>
       <c r="R4" t="n">
-        <v>6957270</v>
+        <v>6957337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533496</v>
+        <v>130533505</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>91795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +992,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1010,7 +1015,7 @@
         <v>454216</v>
       </c>
       <c r="R5" t="n">
-        <v>6957337</v>
+        <v>6957270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,11 +1048,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533497</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533498</v>
       </c>
       <c r="B3" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533496</v>
+        <v>130533505</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>91796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -917,7 +913,7 @@
         <v>454216</v>
       </c>
       <c r="R4" t="n">
-        <v>6957337</v>
+        <v>6957270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +946,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533505</v>
+        <v>130533496</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1015,7 +1010,7 @@
         <v>454216</v>
       </c>
       <c r="R5" t="n">
-        <v>6957270</v>
+        <v>6957337</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,6 +1043,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130533497</v>
+        <v>130533496</v>
       </c>
       <c r="B2" t="n">
-        <v>57878</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454203</v>
+        <v>454216</v>
       </c>
       <c r="R2" t="n">
-        <v>6957252</v>
+        <v>6957337</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130533498</v>
+        <v>130533497</v>
       </c>
       <c r="B3" t="n">
-        <v>57878</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454209</v>
+        <v>454203</v>
       </c>
       <c r="R3" t="n">
-        <v>6957229</v>
+        <v>6957252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533505</v>
+        <v>130533498</v>
       </c>
       <c r="B4" t="n">
-        <v>91822</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454216</v>
+        <v>454209</v>
       </c>
       <c r="R4" t="n">
-        <v>6957270</v>
+        <v>6957229</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +952,11 @@
           <t>2026-01-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -969,108 +978,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>130533496</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57878</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Havsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>454216</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6957337</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62159-2025 artfynd.xlsx
+++ b/artfynd/A 62159-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533498</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>